--- a/data/trans_orig/IP31KM12_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM12_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>120318</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>118068</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100642</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97952</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>99317</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>96713</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>100349</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>134088</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>131434</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>135176</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>315</t>
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>234731</t>
+          <t>219635</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231473</t>
+          <t>216667</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236260</t>
+          <t>221201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>88825</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>83868</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>91447</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>90817</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85938</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>93611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>182534</t>
+          <t>180697</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177029</t>
+          <t>175028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>185234</t>
+          <t>183308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,74 +1406,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49374</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46285</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>51314</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48395</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>52010</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>62334</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>107158</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108478</t>
+          <t>104341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3615</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>3513</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>3944</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>194418</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>189735</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>196611</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>211317</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>205762</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>214027</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>209620</t>
+          <t>172295</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204696</t>
+          <t>166842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>212062</t>
+          <t>174935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>420938</t>
+          <t>366713</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>415002</t>
+          <t>360490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>424705</t>
+          <t>370278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2895</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7578</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4220</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1510</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9775</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>144129</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>139853</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>96,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>111449</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>107429</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>113997</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>93,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>157915</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153539</t>
+          <t>106976</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>113849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>269363</t>
+          <t>255571</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263476</t>
+          <t>250011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272357</t>
+          <t>258592</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5733</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4060</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1512</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>64848</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>60712</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>65074</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>59925</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>67397</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67973</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>133046</t>
+          <t>131232</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127224</t>
+          <t>125063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136186</t>
+          <t>134380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>3821</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1498</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8970</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>669436</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>663419</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>672813</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>875</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>626682</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>618379</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>632649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>725637</t>
+          <t>591569</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>719882</t>
+          <t>582965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>729612</t>
+          <t>597835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1352319</t>
+          <t>1261005</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1342294</t>
+          <t>1252260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1359762</t>
+          <t>1269335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2882</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12482</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26752</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>33667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
